--- a/artfynd/A 3511-2023 artfynd.xlsx
+++ b/artfynd/A 3511-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3511-2023 artfynd.xlsx
+++ b/artfynd/A 3511-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108415209</v>
+        <v>108415145</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>..., Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669035.6441127005</v>
+        <v>669032</v>
       </c>
       <c r="R2" t="n">
-        <v>6706115.064604912</v>
+        <v>6706311</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +751,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108415211</v>
+        <v>113243148</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668952.4726062249</v>
+        <v>668974</v>
       </c>
       <c r="R3" t="n">
-        <v>6706084.007164106</v>
+        <v>6706056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +861,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108415210</v>
+        <v>113246155</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668964.6286571589</v>
+        <v>668942</v>
       </c>
       <c r="R4" t="n">
-        <v>6706131.015868785</v>
+        <v>6706073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +971,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108415170</v>
+        <v>113246158</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,42 +998,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669045.2840127514</v>
+        <v>668978</v>
       </c>
       <c r="R5" t="n">
-        <v>6706162.943860305</v>
+        <v>6706084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,22 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,34 +1066,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>113246159</v>
       </c>
       <c r="B6" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,15 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113246155</v>
+        <v>113246154</v>
       </c>
       <c r="B7" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668942</v>
+        <v>668933</v>
       </c>
       <c r="R7" t="n">
-        <v>6706073</v>
+        <v>6706063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,15 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113246156</v>
+        <v>108415147</v>
       </c>
       <c r="B8" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,34 +1301,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668974</v>
+        <v>668964</v>
       </c>
       <c r="R8" t="n">
-        <v>6706056</v>
+        <v>6706155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,12 +1363,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,31 +1383,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113246157</v>
+        <v>108415149</v>
       </c>
       <c r="B9" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,34 +1406,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668965</v>
+        <v>668955</v>
       </c>
       <c r="R9" t="n">
-        <v>6706082</v>
+        <v>6706090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,12 +1468,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,31 +1488,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113246158</v>
+        <v>108415150</v>
       </c>
       <c r="B10" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,34 +1511,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668978</v>
+        <v>668958</v>
       </c>
       <c r="R10" t="n">
-        <v>6706084</v>
+        <v>6706044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,31 +1593,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108415206</v>
+        <v>108415176</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,34 +1616,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>102613</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>..., Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669209.5994803488</v>
+        <v>668956</v>
       </c>
       <c r="R11" t="n">
-        <v>6706225.957262815</v>
+        <v>6706121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,19 +1689,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,15 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108415208</v>
+        <v>113246157</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,34 +1729,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669171.637588384</v>
+        <v>668965</v>
       </c>
       <c r="R12" t="n">
-        <v>6706286.4308879</v>
+        <v>6706082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,22 +1783,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,27 +1803,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108415205</v>
+        <v>108415170</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,34 +1830,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>..., Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>669243.9638568971</v>
+        <v>669045</v>
       </c>
       <c r="R13" t="n">
-        <v>6706189.523024754</v>
+        <v>6706163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,27 +1895,18 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1998,15 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108415207</v>
+        <v>108415209</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669176.7729262316</v>
+        <v>669036</v>
       </c>
       <c r="R14" t="n">
-        <v>6706271.849970463</v>
+        <v>6706115</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,19 +1993,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,15 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108415202</v>
+        <v>108415210</v>
       </c>
       <c r="B15" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669270.4582348154</v>
+        <v>668965</v>
       </c>
       <c r="R15" t="n">
-        <v>6706056.873020063</v>
+        <v>6706131</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,19 +2090,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,15 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108415204</v>
+        <v>108415211</v>
       </c>
       <c r="B16" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669262.2281218363</v>
+        <v>668952</v>
       </c>
       <c r="R16" t="n">
-        <v>6706158.758182475</v>
+        <v>6706084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,19 +2187,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,15 +2216,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113246166</v>
+        <v>108415212</v>
       </c>
       <c r="B17" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,34 +2227,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669352</v>
+        <v>668960</v>
       </c>
       <c r="R17" t="n">
-        <v>6706131</v>
+        <v>6706027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2404,12 +2281,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2424,31 +2301,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113246163</v>
+        <v>113243158</v>
       </c>
       <c r="B18" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669312</v>
+        <v>669352</v>
       </c>
       <c r="R18" t="n">
-        <v>6706115</v>
+        <v>6706131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,12 +2378,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,6 +2394,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2546,15 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113246165</v>
+        <v>113246163</v>
       </c>
       <c r="B19" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>669343</v>
+        <v>669312</v>
       </c>
       <c r="R19" t="n">
-        <v>6706127</v>
+        <v>6706115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,12 +2523,7 @@
         <v>113246171</v>
       </c>
       <c r="B20" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,15 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113243162</v>
+        <v>113246169</v>
       </c>
       <c r="B21" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,21 +2632,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669396</v>
+        <v>669390</v>
       </c>
       <c r="R21" t="n">
-        <v>6706133</v>
+        <v>6706125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,12 +2686,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,11 +2702,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Cecilia Rätz</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2869,15 +2722,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113246187</v>
+        <v>113246165</v>
       </c>
       <c r="B22" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669295</v>
+        <v>669343</v>
       </c>
       <c r="R22" t="n">
-        <v>6706033</v>
+        <v>6706127</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,15 +2823,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>92231854</v>
+        <v>113246187</v>
       </c>
       <c r="B23" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,16 +2834,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3011,14 +2854,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skatenskogen, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668813.7819832751</v>
+        <v>669295</v>
       </c>
       <c r="R23" t="n">
-        <v>6705779.112063986</v>
+        <v>6706033</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,22 +2888,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,27 +2908,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>92231855</v>
+        <v>108415202</v>
       </c>
       <c r="B24" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,34 +2935,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skatenskogen, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668764.0189416714</v>
+        <v>669271</v>
       </c>
       <c r="R24" t="n">
-        <v>6705795.566670171</v>
+        <v>6706057</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,22 +2989,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,27 +3009,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>92231853</v>
+        <v>108415204</v>
       </c>
       <c r="B25" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3215,34 +3032,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skatenskogen, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668819.8689593319</v>
+        <v>669262</v>
       </c>
       <c r="R25" t="n">
-        <v>6705775.937335981</v>
+        <v>6706159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,22 +3086,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3299,27 +3106,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>108409856</v>
+        <v>108415205</v>
       </c>
       <c r="B26" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3347,17 +3149,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668506.5236493029</v>
+        <v>669244</v>
       </c>
       <c r="R26" t="n">
-        <v>6705660.536876176</v>
+        <v>6706190</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3384,19 +3186,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3411,27 +3203,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>108409858</v>
+        <v>108415206</v>
       </c>
       <c r="B27" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3459,17 +3246,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668388.479731641</v>
+        <v>669209</v>
       </c>
       <c r="R27" t="n">
-        <v>6705421.322440483</v>
+        <v>6706226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3496,19 +3283,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,27 +3300,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>108409853</v>
+        <v>108415207</v>
       </c>
       <c r="B28" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,17 +3343,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668985.6790587006</v>
+        <v>669177</v>
       </c>
       <c r="R28" t="n">
-        <v>6705807.392752416</v>
+        <v>6706272</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3608,19 +3380,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3635,27 +3397,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>108409821</v>
+        <v>108415208</v>
       </c>
       <c r="B29" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,37 +3420,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668583.1734774174</v>
+        <v>669172</v>
       </c>
       <c r="R29" t="n">
-        <v>6705693.752984518</v>
+        <v>6706287</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3720,19 +3477,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3747,27 +3494,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>108409854</v>
+        <v>113243162</v>
       </c>
       <c r="B30" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,17 +3537,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668626.4819316415</v>
+        <v>669396</v>
       </c>
       <c r="R30" t="n">
-        <v>6705752.098212075</v>
+        <v>6706133</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3829,22 +3571,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3855,31 +3587,35 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>108415198</v>
+        <v>113246095</v>
       </c>
       <c r="B31" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,34 +3623,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668981.6375816888</v>
+        <v>668752</v>
       </c>
       <c r="R31" t="n">
-        <v>6705904.539491506</v>
+        <v>6705792</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,22 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,27 +3697,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>108409852</v>
+        <v>113246097</v>
       </c>
       <c r="B32" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,37 +3724,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668972.9605770472</v>
+        <v>668714</v>
       </c>
       <c r="R32" t="n">
-        <v>6705857.196229734</v>
+        <v>6705813</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4053,22 +3778,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,65 +3798,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>108424246</v>
+        <v>113245924</v>
       </c>
       <c r="B33" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668500.6132748567</v>
+        <v>668308</v>
       </c>
       <c r="R33" t="n">
-        <v>6705819.36099925</v>
+        <v>6705620</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4165,22 +3879,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,27 +3899,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>108424227</v>
+        <v>108409786</v>
       </c>
       <c r="B34" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4223,34 +3926,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668524.5468972955</v>
+        <v>668833</v>
       </c>
       <c r="R34" t="n">
-        <v>6705836.78030153</v>
+        <v>6705868</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4280,19 +3991,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4307,27 +4008,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>108424248</v>
+        <v>108409787</v>
       </c>
       <c r="B35" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4335,34 +4031,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668475.1965245216</v>
+        <v>668803</v>
       </c>
       <c r="R35" t="n">
-        <v>6705759.380893675</v>
+        <v>6705850</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4392,19 +4096,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4419,27 +4113,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>108424249</v>
+        <v>108424209</v>
       </c>
       <c r="B36" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4447,34 +4136,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668225.9803289759</v>
+        <v>668778</v>
       </c>
       <c r="R36" t="n">
-        <v>6705616.356604866</v>
+        <v>6705872</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4504,19 +4201,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4543,15 +4230,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>108424244</v>
+        <v>108424214</v>
       </c>
       <c r="B37" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4559,34 +4241,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668851.2274038699</v>
+        <v>668431</v>
       </c>
       <c r="R37" t="n">
-        <v>6705856.949128995</v>
+        <v>6705723</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4616,19 +4306,9 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4655,15 +4335,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>108424242</v>
+        <v>113245929</v>
       </c>
       <c r="B38" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,37 +4346,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skaten, Upl</t>
+          <t>Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668914.8009016124</v>
+        <v>668466</v>
       </c>
       <c r="R38" t="n">
-        <v>6705894.501931747</v>
+        <v>6705773</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4725,22 +4400,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4755,27 +4420,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113245922</v>
+        <v>113245943</v>
       </c>
       <c r="B39" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,21 +4447,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4807,10 +4471,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668326</v>
+        <v>668560</v>
       </c>
       <c r="R39" t="n">
-        <v>6705601</v>
+        <v>6705851</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,15 +4537,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113245929</v>
+        <v>113246093</v>
       </c>
       <c r="B40" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4913,10 +4572,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668466</v>
+        <v>668233</v>
       </c>
       <c r="R40" t="n">
-        <v>6705773</v>
+        <v>6705573</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4979,15 +4638,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113245947</v>
+        <v>92231859</v>
       </c>
       <c r="B41" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,34 +4649,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skatenskogen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668778</v>
+        <v>668409</v>
       </c>
       <c r="R41" t="n">
-        <v>6705808</v>
+        <v>6705859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5049,12 +4703,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5069,31 +4723,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rätz, Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113246095</v>
+        <v>113245944</v>
       </c>
       <c r="B42" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,21 +4746,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3215</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5125,10 +4770,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668752</v>
+        <v>668568</v>
       </c>
       <c r="R42" t="n">
-        <v>6705792</v>
+        <v>6705829</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5155,12 +4800,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5180,7 +4825,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Cecilia Rätz</t>
+          <t>Cecilia Rätz, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5191,50 +4836,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113246097</v>
+        <v>92231858</v>
       </c>
       <c r="B43" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3215</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skatenskogen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668714</v>
+        <v>668412</v>
       </c>
       <c r="R43" t="n">
-        <v>6705813</v>
+        <v>6705894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,12 +4901,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5281,31 +4921,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Axel Linder</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
-        </is>
-      </c>
+          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113246093</v>
+        <v>108409821</v>
       </c>
       <c r="B44" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,37 +4944,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Göksnåre, Upl</t>
+          <t>Skaten, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668233</v>
+        <v>668583</v>
       </c>
       <c r="R44" t="n">
-        <v>6705573</v>
+        <v>6705693</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5367,12 +4998,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,15 +5018,1963 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>108424227</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>668524</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6705837</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>113245932</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Göksnåre, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>668414</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6705863</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Axel Linder</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Dennis Nyström, Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>92231853</v>
+      </c>
+      <c r="B47" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skatenskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>668820</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6705776</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>92231854</v>
+      </c>
+      <c r="B48" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skatenskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>668814</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6705779</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>92231855</v>
+      </c>
+      <c r="B49" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skatenskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>668764</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6705796</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren, Barbara Kühn, Julian Klein, Louis Mielke</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>108409852</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>668973</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6705857</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>108409853</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>668985</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6705808</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>108409854</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>668626</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6705752</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>108409856</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>668507</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6705661</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>108409858</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>668388</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6705421</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Isac Carlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>108415198</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>668981</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6705904</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>108415199</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>..., Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>669045</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6705922</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>108424242</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>668915</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6705895</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>108424244</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>668851</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6705857</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>108424246</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>668500</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6705820</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>108424248</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>668475</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6705759</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>108424249</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>668226</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6705616</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>108424251</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>668194</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6705636</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>113245922</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Göksnåre, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>668326</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6705601</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>113245947</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Göksnåre, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>668778</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6705808</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
         <is>
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>

--- a/artfynd/A 3511-2023 artfynd.xlsx
+++ b/artfynd/A 3511-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415145</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113243148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246158</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246159</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246154</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415147</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415149</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415150</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415176</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246157</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415170</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415209</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2213,6 +2288,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415211</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2310,6 +2390,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415212</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113243158</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246163</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246171</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246169</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246165</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246187</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415202</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3115,6 +3235,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415204</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3212,6 +3337,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415205</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3309,6 +3439,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415206</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3406,6 +3541,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415207</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3503,6 +3643,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415208</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113243162</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3710,6 +3860,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246095</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3811,6 +3966,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246097</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3912,6 +4072,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245924</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4017,6 +4182,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409786</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4122,6 +4292,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409787</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4227,6 +4402,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424209</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4332,6 +4512,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424214</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4433,6 +4618,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245929</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4534,6 +4724,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245943</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4635,6 +4830,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113246093</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4732,6 +4932,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92231859</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4833,6 +5038,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245944</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4930,6 +5140,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92231858</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5027,6 +5242,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409821</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5124,6 +5344,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424227</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5225,6 +5450,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245932</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5322,6 +5552,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92231853</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5419,6 +5654,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92231854</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5516,6 +5756,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92231855</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5613,6 +5858,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409852</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5710,6 +5960,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409853</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5807,6 +6062,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409854</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5904,6 +6164,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409856</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6001,6 +6266,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108409858</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6098,6 +6368,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415198</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6195,6 +6470,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108415199</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6292,6 +6572,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424242</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6389,6 +6674,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424244</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6486,6 +6776,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424246</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6583,6 +6878,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424248</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6680,6 +6980,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424249</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6777,6 +7082,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108424251</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6878,6 +7188,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245922</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6979,8 +7294,78 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>